--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2022_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2022_coquimbo.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:38</t>
+    <t xml:space="preserve">2026-09-24 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -730,19 +730,19 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.25</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="11">
@@ -756,13 +756,13 @@
         <v>-0.19</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0.14</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.33</v>
@@ -776,19 +776,19 @@
         <v>19</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="13">
@@ -799,19 +799,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -845,19 +845,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.11</v>
+        <v>0.45</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.07</v>
+        <v>0.29</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>332</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="16">
@@ -868,19 +868,19 @@
         <v>25</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.53</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>332</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="17">
@@ -891,19 +891,19 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.71</v>
+        <v>-0.69</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>332</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
